--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_valparaiso.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>23.93019102708951</v>
+      </c>
+      <c r="C2">
         <v>36.1722732171586</v>
-      </c>
-      <c r="C2">
-        <v>23.93019102708951</v>
       </c>
       <c r="D2">
         <v>2.76454839870457</v>
       </c>
       <c r="E2">
-        <v>22.59320203964827</v>
+        <v>14.9467974400333</v>
       </c>
       <c r="F2">
         <v>62.46000052031844</v>
       </c>
       <c r="G2">
-        <v>14.9467974400333</v>
+        <v>22.59320203964827</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.05759622247845</v>
+      </c>
+      <c r="C3">
         <v>32.31208477461154</v>
-      </c>
-      <c r="C3">
-        <v>27.05759622247845</v>
       </c>
       <c r="D3">
         <v>3.09481733220051</v>
       </c>
       <c r="E3">
-        <v>20.27492592847791</v>
+        <v>16.97788189898711</v>
       </c>
       <c r="F3">
         <v>62.74719217253497</v>
       </c>
       <c r="G3">
-        <v>16.97788189898711</v>
+        <v>20.27492592847791</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>24.73881463301383</v>
+      </c>
+      <c r="C4">
         <v>32.26095320221552</v>
-      </c>
-      <c r="C4">
-        <v>24.73881463301383</v>
       </c>
       <c r="D4">
         <v>3.099722422123985</v>
       </c>
       <c r="E4">
-        <v>20.5484082218983</v>
+        <v>15.75723007372668</v>
       </c>
       <c r="F4">
         <v>63.69436170437501</v>
       </c>
       <c r="G4">
-        <v>15.75723007372668</v>
+        <v>20.5484082218983</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>35.85951940850277</v>
+      </c>
+      <c r="C5">
         <v>30.31423290203327</v>
-      </c>
-      <c r="C5">
-        <v>35.85951940850277</v>
       </c>
       <c r="D5">
         <v>3.298780487804878</v>
       </c>
       <c r="E5">
-        <v>18.24249165739711</v>
+        <v>21.57953281423804</v>
       </c>
       <c r="F5">
         <v>60.17797552836485</v>
       </c>
       <c r="G5">
-        <v>21.57953281423804</v>
+        <v>18.24249165739711</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.32756586708612</v>
+      </c>
+      <c r="C6">
         <v>37.62485253637436</v>
-      </c>
-      <c r="C6">
-        <v>29.32756586708612</v>
       </c>
       <c r="D6">
         <v>2.657817725752508</v>
       </c>
       <c r="E6">
-        <v>22.53627284718297</v>
+        <v>17.5664217071792</v>
       </c>
       <c r="F6">
         <v>59.89730544563783</v>
       </c>
       <c r="G6">
-        <v>17.5664217071792</v>
+        <v>22.53627284718297</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.52732349421619</v>
+      </c>
+      <c r="C7">
         <v>35.22636617471081</v>
-      </c>
-      <c r="C7">
-        <v>29.52732349421619</v>
       </c>
       <c r="D7">
         <v>2.838782731776362</v>
       </c>
       <c r="E7">
-        <v>21.38123051781012</v>
+        <v>17.92210150410071</v>
       </c>
       <c r="F7">
         <v>60.69666797808915</v>
       </c>
       <c r="G7">
-        <v>17.92210150410071</v>
+        <v>21.38123051781012</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>23.4208490474809</v>
+      </c>
+      <c r="C8">
         <v>38.67469296973213</v>
-      </c>
-      <c r="C8">
-        <v>23.4208490474809</v>
       </c>
       <c r="D8">
         <v>2.585670171402853</v>
       </c>
       <c r="E8">
-        <v>23.85919593373225</v>
+        <v>14.44879282676005</v>
       </c>
       <c r="F8">
         <v>61.69201123950771</v>
       </c>
       <c r="G8">
-        <v>14.44879282676005</v>
+        <v>23.85919593373225</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>30.51381932851048</v>
+      </c>
+      <c r="C9">
         <v>17.49211649044704</v>
-      </c>
-      <c r="C9">
-        <v>30.51381932851048</v>
       </c>
       <c r="D9">
         <v>5.716861081654295</v>
       </c>
       <c r="E9">
-        <v>11.81852362451435</v>
+        <v>20.6166186238877</v>
       </c>
       <c r="F9">
         <v>67.56485775159794</v>
       </c>
       <c r="G9">
-        <v>20.6166186238877</v>
+        <v>11.81852362451435</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.45119524300477</v>
+      </c>
+      <c r="C10">
         <v>33.86481885534802</v>
-      </c>
-      <c r="C10">
-        <v>26.45119524300477</v>
       </c>
       <c r="D10">
         <v>2.95291702067403</v>
       </c>
       <c r="E10">
-        <v>21.12379043716256</v>
+        <v>16.49940923978882</v>
       </c>
       <c r="F10">
-        <v>62.37680032304863</v>
+        <v>62.37680032304861</v>
       </c>
       <c r="G10">
-        <v>16.49940923978883</v>
+        <v>21.12379043716255</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>31.43361361984844</v>
+      </c>
+      <c r="C11">
         <v>27.95598463614658</v>
-      </c>
-      <c r="C11">
-        <v>31.43361361984844</v>
       </c>
       <c r="D11">
         <v>3.577051615298923</v>
       </c>
       <c r="E11">
-        <v>17.53940341279145</v>
+        <v>19.72124527810342</v>
       </c>
       <c r="F11">
         <v>62.73935130910512</v>
       </c>
       <c r="G11">
-        <v>19.72124527810342</v>
+        <v>17.53940341279145</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>30.50796513375413</v>
+      </c>
+      <c r="C12">
         <v>30.40276525398257</v>
-      </c>
-      <c r="C12">
-        <v>30.50796513375413</v>
       </c>
       <c r="D12">
         <v>3.289174493326743</v>
       </c>
       <c r="E12">
+        <v>18.95955916690016</v>
+      </c>
+      <c r="F12">
+        <v>62.14625945643038</v>
+      </c>
+      <c r="G12">
         <v>18.89418137666947</v>
-      </c>
-      <c r="F12">
-        <v>62.14625945643036</v>
-      </c>
-      <c r="G12">
-        <v>18.95955916690016</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>29.43933197000682</v>
+      </c>
+      <c r="C13">
         <v>32.74539877300614</v>
-      </c>
-      <c r="C13">
-        <v>29.43933197000682</v>
       </c>
       <c r="D13">
         <v>3.053864168618267</v>
       </c>
       <c r="E13">
-        <v>20.19018598297783</v>
+        <v>18.15172848586739</v>
       </c>
       <c r="F13">
         <v>61.65808553115478</v>
       </c>
       <c r="G13">
-        <v>18.15172848586739</v>
+        <v>20.19018598297783</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.64364079642422</v>
+      </c>
+      <c r="C14">
         <v>35.43275091426249</v>
-      </c>
-      <c r="C14">
-        <v>26.64364079642422</v>
       </c>
       <c r="D14">
         <v>2.822247706422018</v>
       </c>
       <c r="E14">
-        <v>21.86175947050417</v>
+        <v>16.43894000551558</v>
       </c>
       <c r="F14">
         <v>61.69930052398024</v>
       </c>
       <c r="G14">
-        <v>16.43894000551558</v>
+        <v>21.86175947050417</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.36349550666254</v>
+      </c>
+      <c r="C15">
         <v>33.54508831732259</v>
-      </c>
-      <c r="C15">
-        <v>26.36349550666254</v>
       </c>
       <c r="D15">
         <v>2.981062355658199</v>
       </c>
       <c r="E15">
-        <v>20.97766581076498</v>
+        <v>16.48660433118551</v>
       </c>
       <c r="F15">
-        <v>62.53572985804951</v>
+        <v>62.53572985804952</v>
       </c>
       <c r="G15">
-        <v>16.48660433118551</v>
+        <v>20.97766581076499</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>25.63421116211645</v>
+      </c>
+      <c r="C16">
         <v>37.01377144237738</v>
-      </c>
-      <c r="C16">
-        <v>25.63421116211645</v>
       </c>
       <c r="D16">
         <v>2.701697127937337</v>
       </c>
       <c r="E16">
-        <v>22.75698158051099</v>
+        <v>15.76054664289958</v>
       </c>
       <c r="F16">
         <v>61.48247177658942</v>
       </c>
       <c r="G16">
-        <v>15.76054664289958</v>
+        <v>22.75698158051099</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.67894824987439</v>
+      </c>
+      <c r="C17">
         <v>39.49087255066154</v>
-      </c>
-      <c r="C17">
-        <v>26.67894824987439</v>
       </c>
       <c r="D17">
         <v>2.532230703986429</v>
       </c>
       <c r="E17">
-        <v>23.76536988510381</v>
+        <v>16.05523080024188</v>
       </c>
       <c r="F17">
         <v>60.1793993146543</v>
       </c>
       <c r="G17">
-        <v>16.05523080024188</v>
+        <v>23.76536988510381</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.69943983001739</v>
+      </c>
+      <c r="C18">
         <v>38.34266949971025</v>
-      </c>
-      <c r="C18">
-        <v>27.69943983001739</v>
       </c>
       <c r="D18">
         <v>2.608060453400504</v>
       </c>
       <c r="E18">
-        <v>23.09213587715216</v>
+        <v>16.68217775709633</v>
       </c>
       <c r="F18">
-        <v>60.22568636575151</v>
+        <v>60.22568636575152</v>
       </c>
       <c r="G18">
-        <v>16.68217775709632</v>
+        <v>23.09213587715217</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>25.28211365632813</v>
+      </c>
+      <c r="C19">
         <v>35.03952969795257</v>
-      </c>
-      <c r="C19">
-        <v>25.28211365632813</v>
       </c>
       <c r="D19">
         <v>2.853919583453862</v>
       </c>
       <c r="E19">
-        <v>21.8557700413049</v>
+        <v>15.76961982635084</v>
       </c>
       <c r="F19">
         <v>62.37461013234427</v>
       </c>
       <c r="G19">
-        <v>15.76961982635084</v>
+        <v>21.8557700413049</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>29.20939294503692</v>
+      </c>
+      <c r="C20">
         <v>23.05168170631665</v>
-      </c>
-      <c r="C20">
-        <v>29.20939294503692</v>
       </c>
       <c r="D20">
         <v>4.338078291814947</v>
       </c>
       <c r="E20">
-        <v>15.13957638818736</v>
+        <v>19.18375593494292</v>
       </c>
       <c r="F20">
         <v>65.67666767686971</v>
       </c>
       <c r="G20">
-        <v>19.18375593494292</v>
+        <v>15.13957638818736</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>25.86155894098506</v>
+      </c>
+      <c r="C21">
         <v>30.7868658482473</v>
-      </c>
-      <c r="C21">
-        <v>25.86155894098506</v>
       </c>
       <c r="D21">
         <v>3.248138361758347</v>
       </c>
       <c r="E21">
-        <v>19.6534793692758</v>
+        <v>16.50930034935323</v>
       </c>
       <c r="F21">
         <v>63.83722028137097</v>
       </c>
       <c r="G21">
-        <v>16.50930034935323</v>
+        <v>19.6534793692758</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>29.91746450973919</v>
+      </c>
+      <c r="C22">
         <v>28.8412017167382</v>
-      </c>
-      <c r="C22">
-        <v>29.91746450973919</v>
       </c>
       <c r="D22">
         <v>3.467261904761905</v>
       </c>
       <c r="E22">
+        <v>18.84461819996672</v>
+      </c>
+      <c r="F22">
+        <v>62.98868740642155</v>
+      </c>
+      <c r="G22">
         <v>18.16669439361171</v>
-      </c>
-      <c r="F22">
-        <v>62.98868740642156</v>
-      </c>
-      <c r="G22">
-        <v>18.84461819996673</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.45041471330689</v>
+      </c>
+      <c r="C23">
         <v>38.21132347637937</v>
-      </c>
-      <c r="C23">
-        <v>27.45041471330689</v>
       </c>
       <c r="D23">
         <v>2.617025292563231</v>
       </c>
       <c r="E23">
-        <v>23.06587139187601</v>
+        <v>16.57015978057382</v>
       </c>
       <c r="F23">
         <v>60.36396882755018</v>
       </c>
       <c r="G23">
-        <v>16.57015978057382</v>
+        <v>23.06587139187601</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>26.66844678827122</v>
+      </c>
+      <c r="C24">
         <v>34.40196258406903</v>
-      </c>
-      <c r="C24">
-        <v>26.66844678827122</v>
       </c>
       <c r="D24">
         <v>2.906810905210051</v>
       </c>
       <c r="E24">
-        <v>21.3583380821634</v>
+        <v>16.55701186344092</v>
       </c>
       <c r="F24">
         <v>62.08465005439569</v>
       </c>
       <c r="G24">
-        <v>16.55701186344092</v>
+        <v>21.3583380821634</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.49369641956632</v>
+      </c>
+      <c r="C25">
         <v>50.2773575390822</v>
-      </c>
-      <c r="C25">
-        <v>27.49369641956632</v>
       </c>
       <c r="D25">
         <v>1.988966900702106</v>
       </c>
       <c r="E25">
-        <v>28.2820832860547</v>
+        <v>15.46578917508227</v>
       </c>
       <c r="F25">
         <v>56.25212753886304</v>
       </c>
       <c r="G25">
-        <v>15.46578917508227</v>
+        <v>28.2820832860547</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>29.20862336960194</v>
+      </c>
+      <c r="C26">
         <v>43.5290937352166</v>
-      </c>
-      <c r="C26">
-        <v>29.20862336960194</v>
       </c>
       <c r="D26">
         <v>2.297314081664338</v>
       </c>
       <c r="E26">
-        <v>25.19953051643192</v>
+        <v>16.90923317683881</v>
       </c>
       <c r="F26">
         <v>57.89123630672926</v>
       </c>
       <c r="G26">
-        <v>16.90923317683881</v>
+        <v>25.19953051643192</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>26.83765449307685</v>
+      </c>
+      <c r="C27">
         <v>51.54725397267912</v>
-      </c>
-      <c r="C27">
-        <v>26.83765449307685</v>
       </c>
       <c r="D27">
         <v>1.939967550027042</v>
       </c>
       <c r="E27">
-        <v>28.896645134403</v>
+        <v>15.04480100020838</v>
       </c>
       <c r="F27">
         <v>56.05855386538862</v>
       </c>
       <c r="G27">
-        <v>15.04480100020838</v>
+        <v>28.896645134403</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.0696168948318</v>
+      </c>
+      <c r="C28">
         <v>53.86819484240688</v>
-      </c>
-      <c r="C28">
-        <v>28.0696168948318</v>
       </c>
       <c r="D28">
         <v>1.856382978723404</v>
       </c>
       <c r="E28">
+        <v>15.42813812412506</v>
+      </c>
+      <c r="F28">
+        <v>54.96383574428371</v>
+      </c>
+      <c r="G28">
         <v>29.60802613159123</v>
-      </c>
-      <c r="F28">
-        <v>54.96383574428372</v>
-      </c>
-      <c r="G28">
-        <v>15.42813812412506</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.14152094347296</v>
+      </c>
+      <c r="C29">
         <v>37.34580452758574</v>
-      </c>
-      <c r="C29">
-        <v>28.14152094347296</v>
       </c>
       <c r="D29">
         <v>2.677676950998185</v>
       </c>
       <c r="E29">
-        <v>22.56716906946265</v>
+        <v>17.00524246395807</v>
       </c>
       <c r="F29">
         <v>60.42758846657929</v>
       </c>
       <c r="G29">
-        <v>17.00524246395806</v>
+        <v>22.56716906946265</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>27.7140110267428</v>
+      </c>
+      <c r="C30">
         <v>30.61785076618204</v>
-      </c>
-      <c r="C30">
-        <v>27.7140110267428</v>
       </c>
       <c r="D30">
         <v>3.266068567766741</v>
       </c>
       <c r="E30">
-        <v>19.33776968164864</v>
+        <v>17.50374859040609</v>
       </c>
       <c r="F30">
         <v>63.15848172794528</v>
       </c>
       <c r="G30">
-        <v>17.50374859040609</v>
+        <v>19.33776968164864</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>27.59449421018134</v>
+      </c>
+      <c r="C31">
         <v>34.42211055276382</v>
-      </c>
-      <c r="C31">
-        <v>27.59449421018134</v>
       </c>
       <c r="D31">
         <v>2.905109489051095</v>
       </c>
       <c r="E31">
+        <v>17.03189265727193</v>
+      </c>
+      <c r="F31">
+        <v>61.72206864001079</v>
+      </c>
+      <c r="G31">
         <v>21.24603870271728</v>
-      </c>
-      <c r="F31">
-        <v>61.72206864001078</v>
-      </c>
-      <c r="G31">
-        <v>17.03189265727193</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>31.20088544548976</v>
+      </c>
+      <c r="C32">
         <v>18.74930824571112</v>
-      </c>
-      <c r="C32">
-        <v>31.20088544548976</v>
       </c>
       <c r="D32">
         <v>5.333530106257379</v>
       </c>
       <c r="E32">
-        <v>12.50369058163567</v>
+        <v>20.80749926188367</v>
       </c>
       <c r="F32">
         <v>66.68881015648066</v>
       </c>
       <c r="G32">
-        <v>20.80749926188367</v>
+        <v>12.50369058163567</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>25.94594594594595</v>
+      </c>
+      <c r="C33">
         <v>32.5987525987526</v>
-      </c>
-      <c r="C33">
-        <v>25.94594594594595</v>
       </c>
       <c r="D33">
         <v>3.067602040816327</v>
       </c>
       <c r="E33">
-        <v>20.56123787044323</v>
+        <v>16.36506687647521</v>
       </c>
       <c r="F33">
-        <v>63.07369525308157</v>
+        <v>63.07369525308156</v>
       </c>
       <c r="G33">
-        <v>16.36506687647522</v>
+        <v>20.56123787044322</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>28.55930605317745</v>
+      </c>
+      <c r="C34">
         <v>38.22364699226853</v>
-      </c>
-      <c r="C34">
-        <v>28.55930605317745</v>
       </c>
       <c r="D34">
         <v>2.616181549087321</v>
       </c>
       <c r="E34">
-        <v>22.91819775001413</v>
+        <v>17.12363615806434</v>
       </c>
       <c r="F34">
         <v>59.95816609192153</v>
       </c>
       <c r="G34">
-        <v>17.12363615806434</v>
+        <v>22.91819775001413</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>29.23606484565845</v>
+      </c>
+      <c r="C35">
         <v>34.14390406395736</v>
-      </c>
-      <c r="C35">
-        <v>29.23606484565845</v>
       </c>
       <c r="D35">
         <v>2.928780487804878</v>
       </c>
       <c r="E35">
-        <v>20.89846404784559</v>
+        <v>17.8945222237325</v>
       </c>
       <c r="F35">
         <v>61.20701372842191</v>
       </c>
       <c r="G35">
-        <v>17.8945222237325</v>
+        <v>20.89846404784559</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>24.50491607905452</v>
+      </c>
+      <c r="C36">
         <v>38.25504022246499</v>
-      </c>
-      <c r="C36">
-        <v>24.50491607905452</v>
       </c>
       <c r="D36">
         <v>2.614034632259405</v>
       </c>
       <c r="E36">
+        <v>15.0558630242307</v>
+      </c>
+      <c r="F36">
+        <v>61.44017378251558</v>
+      </c>
+      <c r="G36">
         <v>23.50396319325372</v>
-      </c>
-      <c r="F36">
-        <v>61.44017378251556</v>
-      </c>
-      <c r="G36">
-        <v>15.0558630242307</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>27.09647351250582</v>
+      </c>
+      <c r="C37">
         <v>34.60929004194501</v>
-      </c>
-      <c r="C37">
-        <v>27.09647351250582</v>
       </c>
       <c r="D37">
         <v>2.889397611993895</v>
       </c>
       <c r="E37">
+        <v>16.75665289653184</v>
+      </c>
+      <c r="F37">
+        <v>61.84071476606782</v>
+      </c>
+      <c r="G37">
         <v>21.40263233740033</v>
-      </c>
-      <c r="F37">
-        <v>61.84071476606783</v>
-      </c>
-      <c r="G37">
-        <v>16.75665289653185</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>27.48872702046479</v>
+      </c>
+      <c r="C38">
         <v>42.00485605272286</v>
-      </c>
-      <c r="C38">
-        <v>27.48872702046479</v>
       </c>
       <c r="D38">
         <v>2.380677126341866</v>
       </c>
       <c r="E38">
-        <v>24.78256420751049</v>
+        <v>16.21815205157065</v>
       </c>
       <c r="F38">
         <v>58.99928374091886</v>
       </c>
       <c r="G38">
-        <v>16.21815205157065</v>
+        <v>24.78256420751049</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>28.20278042867092</v>
+      </c>
+      <c r="C39">
         <v>36.00500373990869</v>
-      </c>
-      <c r="C39">
-        <v>28.20278042867092</v>
       </c>
       <c r="D39">
         <v>2.777391740391848</v>
       </c>
       <c r="E39">
-        <v>21.92649022225713</v>
+        <v>17.17505693866332</v>
       </c>
       <c r="F39">
         <v>60.89845283907956</v>
       </c>
       <c r="G39">
-        <v>17.17505693866332</v>
+        <v>21.92649022225713</v>
       </c>
     </row>
   </sheetData>
